--- a/Output/kpss_weekly.xlsx
+++ b/Output/kpss_weekly.xlsx
@@ -966,7 +966,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
